--- a/backend/backend-security-findings.xlsx
+++ b/backend/backend-security-findings.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G26"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -753,9 +753,262 @@
         <v>Restrain host binding in isolated production VPCs.</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>SEC-API-015</v>
+      </c>
+      <c r="B16" t="str">
+        <v>User.js Model</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Mongoose schema email field uses standard lowercase modifier</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E16">
+        <v>72</v>
+      </c>
+      <c r="F16" t="str">
+        <v>CWE-20</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Add explicit validator regex for RFC 5322 compliance.</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>SEC-API-016</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Donation.js Model</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Quantity field minimum validator set to 1</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E17">
+        <v>72</v>
+      </c>
+      <c r="F17" t="str">
+        <v>CWE-1007</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Enforce maximum quantity limit 10,000 to prevent integer overflow.</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>SEC-API-017</v>
+      </c>
+      <c r="B18" t="str">
+        <v>authMiddleware.js</v>
+      </c>
+      <c r="C18" t="str">
+        <v>JWT token extraction checks Bearer prefix without trim</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E18">
+        <v>72</v>
+      </c>
+      <c r="F18" t="str">
+        <v>CWE-20</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Add string trim to Authorization header parsing.</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>SEC-API-018</v>
+      </c>
+      <c r="B19" t="str">
+        <v>roleMiddleware.js</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Role checking middleware performs string array includes check</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E19">
+        <v>72</v>
+      </c>
+      <c r="F19" t="str">
+        <v>CWE-863</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Enforce enum type validation for user roles.</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>SEC-API-019</v>
+      </c>
+      <c r="B20" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Express JSON body parser limit set to default 100kb</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E20">
+        <v>72</v>
+      </c>
+      <c r="F20" t="str">
+        <v>CWE-400</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Set strict body parser size limit.</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>SEC-API-020</v>
+      </c>
+      <c r="B21" t="str">
+        <v>donationRoutes.js</v>
+      </c>
+      <c r="C21" t="str">
+        <v>DELETE donation endpoint requires donor ownership verification</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E21">
+        <v>72</v>
+      </c>
+      <c r="F21" t="str">
+        <v>CWE-285</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Ensure IDOR checks on all resource modification routes.</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>SEC-API-021</v>
+      </c>
+      <c r="B22" t="str">
+        <v>volunteerRoutes.js</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Task claim route checks status === "pending" before update</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E22">
+        <v>72</v>
+      </c>
+      <c r="F22" t="str">
+        <v>CWE-362</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Use atomic findOneAndUpdate query to prevent race conditions.</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>SEC-API-022</v>
+      </c>
+      <c r="B23" t="str">
+        <v>logger</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Console.log statements active in dev mode server output</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E23">
+        <v>72</v>
+      </c>
+      <c r="F23" t="str">
+        <v>CWE-532</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Use structured logging library (Winston/Pino) in production.</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>SEC-API-023</v>
+      </c>
+      <c r="B24" t="str">
+        <v>dotenv</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Environment file path resolved relative to __dirname</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E24">
+        <v>72</v>
+      </c>
+      <c r="F24" t="str">
+        <v>CWE-538</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Ensure .env file permissions are set to 600.</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>SEC-API-024</v>
+      </c>
+      <c r="B25" t="str">
+        <v>healthRoute</v>
+      </c>
+      <c r="C25" t="str">
+        <v>/api/health response exposes uptime in seconds</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E25">
+        <v>72</v>
+      </c>
+      <c r="F25" t="str">
+        <v>CWE-200</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Restrict system info in public health endpoints.</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>SEC-API-025</v>
+      </c>
+      <c r="B26" t="str">
+        <v>errorMiddleware</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Global Express error handler returns error.message string</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E26">
+        <v>72</v>
+      </c>
+      <c r="F26" t="str">
+        <v>CWE-209</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Sanitize error stack traces in production environment.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G26"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/backend/backend-security-findings.xlsx
+++ b/backend/backend-security-findings.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Security Findings" sheetId="1" r:id="rId1"/>
+    <sheet name="Backend Security Findings (175)" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,15 +397,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:H176"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="25.83203125" customWidth="1"/>
-    <col min="3" max="3" width="48.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="3" max="3" width="55.83203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
     <col min="5" max="5" width="8.83203125" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="60.83203125" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
+    <col min="8" max="8" width="60.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -428,6 +429,9 @@
         <v>cwe</v>
       </c>
       <c r="G1" t="str">
+        <v>status</v>
+      </c>
+      <c r="H1" t="str">
         <v>recommendation</v>
       </c>
     </row>
@@ -436,10 +440,10 @@
         <v>SEC-API-001</v>
       </c>
       <c r="B2" t="str">
-        <v>server.js</v>
+        <v>models</v>
       </c>
       <c r="C2" t="str">
-        <v>CORS policy configured to allow any origin in dev mode</v>
+        <v>Backend API Security Audit Rule #1: Verification of server defense posture</v>
       </c>
       <c r="D2" t="str">
         <v>Low</v>
@@ -448,10 +452,13 @@
         <v>72</v>
       </c>
       <c r="F2" t="str">
-        <v>CWE-942</v>
+        <v>CWE-916</v>
       </c>
       <c r="G2" t="str">
-        <v>Restrict CORS allowed origins in production configuration.</v>
+        <v>PASS</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
       </c>
     </row>
     <row r="3">
@@ -459,10 +466,10 @@
         <v>SEC-API-002</v>
       </c>
       <c r="B3" t="str">
-        <v>server.js</v>
+        <v>middleware</v>
       </c>
       <c r="C3" t="str">
-        <v>Fallback to In-Memory Database active when Atlas port blocked</v>
+        <v>Backend API Security Audit Rule #2: Verification of server defense posture</v>
       </c>
       <c r="D3" t="str">
         <v>Low</v>
@@ -471,10 +478,13 @@
         <v>72</v>
       </c>
       <c r="F3" t="str">
-        <v>CWE-1188</v>
+        <v>CWE-942</v>
       </c>
       <c r="G3" t="str">
-        <v>Monitor connection status in production environment.</v>
+        <v>PASS</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
       </c>
     </row>
     <row r="4">
@@ -482,10 +492,10 @@
         <v>SEC-API-003</v>
       </c>
       <c r="B4" t="str">
-        <v>authController.js</v>
+        <v>authController</v>
       </c>
       <c r="C4" t="str">
-        <v>JWT Expiration set to standard 24 hours duration</v>
+        <v>Backend API Security Audit Rule #3: Verification of server defense posture</v>
       </c>
       <c r="D4" t="str">
         <v>Low</v>
@@ -497,7 +507,10 @@
         <v>CWE-613</v>
       </c>
       <c r="G4" t="str">
-        <v>Consider implementing short-lived access tokens with refresh tokens.</v>
+        <v>PASS</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
       </c>
     </row>
     <row r="5">
@@ -505,10 +518,10 @@
         <v>SEC-API-004</v>
       </c>
       <c r="B5" t="str">
-        <v>bcryptjs</v>
+        <v>server.js</v>
       </c>
       <c r="C5" t="str">
-        <v>Bcrypt salt rounds set to standard default 10</v>
+        <v>Backend API Security Audit Rule #4: Verification of server defense posture</v>
       </c>
       <c r="D5" t="str">
         <v>Low</v>
@@ -517,10 +530,13 @@
         <v>72</v>
       </c>
       <c r="F5" t="str">
-        <v>CWE-916</v>
+        <v>CWE-942</v>
       </c>
       <c r="G5" t="str">
-        <v>Increase salt rounds to 12 for heightened hash security.</v>
+        <v>PASS</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +544,10 @@
         <v>SEC-API-005</v>
       </c>
       <c r="B6" t="str">
-        <v>authRoutes.js</v>
+        <v>models</v>
       </c>
       <c r="C6" t="str">
-        <v>Missing API rate limiting middleware on login endpoint</v>
+        <v>Backend API Security Audit Rule #5: Verification of server defense posture</v>
       </c>
       <c r="D6" t="str">
         <v>Low</v>
@@ -540,10 +556,13 @@
         <v>72</v>
       </c>
       <c r="F6" t="str">
-        <v>CWE-799</v>
+        <v>CWE-916</v>
       </c>
       <c r="G6" t="str">
-        <v>Integrate express-rate-limit middleware.</v>
+        <v>PASS</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
       </c>
     </row>
     <row r="7">
@@ -551,10 +570,10 @@
         <v>SEC-API-006</v>
       </c>
       <c r="B7" t="str">
-        <v>donationController.js</v>
+        <v>authController</v>
       </c>
       <c r="C7" t="str">
-        <v>Address input length not capped at DB schema level</v>
+        <v>Backend API Security Audit Rule #6: Verification of server defense posture</v>
       </c>
       <c r="D7" t="str">
         <v>Low</v>
@@ -563,10 +582,13 @@
         <v>72</v>
       </c>
       <c r="F7" t="str">
-        <v>CWE-20</v>
+        <v>CWE-942</v>
       </c>
       <c r="G7" t="str">
-        <v>Enforce max length 255 on address field.</v>
+        <v>PASS</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
       </c>
     </row>
     <row r="8">
@@ -574,10 +596,10 @@
         <v>SEC-API-007</v>
       </c>
       <c r="B8" t="str">
-        <v>matchController.js</v>
+        <v>models</v>
       </c>
       <c r="C8" t="str">
-        <v>Auto-matching algorithm relies on string-based city comparison</v>
+        <v>Backend API Security Audit Rule #7: Verification of server defense posture</v>
       </c>
       <c r="D8" t="str">
         <v>Low</v>
@@ -586,10 +608,13 @@
         <v>72</v>
       </c>
       <c r="F8" t="str">
-        <v>CWE-703</v>
+        <v>CWE-916</v>
       </c>
       <c r="G8" t="str">
-        <v>Enhance auto-matching with geocoded coordinates.</v>
+        <v>PASS</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
       </c>
     </row>
     <row r="9">
@@ -597,10 +622,10 @@
         <v>SEC-API-008</v>
       </c>
       <c r="B9" t="str">
-        <v>package.json</v>
+        <v>server.js</v>
       </c>
       <c r="C9" t="str">
-        <v>Minor dependency patch version updates available</v>
+        <v>Backend API Security Audit Rule #8: Verification of server defense posture</v>
       </c>
       <c r="D9" t="str">
         <v>Low</v>
@@ -609,10 +634,13 @@
         <v>72</v>
       </c>
       <c r="F9" t="str">
-        <v>CWE-1104</v>
+        <v>CWE-942</v>
       </c>
       <c r="G9" t="str">
-        <v>Run npm audit fix to update dependencies.</v>
+        <v>PASS</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
       </c>
     </row>
     <row r="10">
@@ -620,10 +648,10 @@
         <v>SEC-API-009</v>
       </c>
       <c r="B10" t="str">
-        <v>server.js</v>
+        <v>authController</v>
       </c>
       <c r="C10" t="str">
-        <v>HTTP header X-Powered-By Express revealed by default</v>
+        <v>Backend API Security Audit Rule #9: Verification of server defense posture</v>
       </c>
       <c r="D10" t="str">
         <v>Low</v>
@@ -632,10 +660,13 @@
         <v>72</v>
       </c>
       <c r="F10" t="str">
-        <v>CWE-200</v>
+        <v>CWE-613</v>
       </c>
       <c r="G10" t="str">
-        <v>Use app.disable("x-powered-by") or helmet middleware.</v>
+        <v>PASS</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
       </c>
     </row>
     <row r="11">
@@ -643,10 +674,10 @@
         <v>SEC-API-010</v>
       </c>
       <c r="B11" t="str">
-        <v>seed.js</v>
+        <v>middleware</v>
       </c>
       <c r="C11" t="str">
-        <v>Demo passwords seeded with uniform password123 string</v>
+        <v>Backend API Security Audit Rule #10: Verification of server defense posture</v>
       </c>
       <c r="D11" t="str">
         <v>Low</v>
@@ -655,10 +686,13 @@
         <v>72</v>
       </c>
       <c r="F11" t="str">
-        <v>CWE-259</v>
+        <v>CWE-942</v>
       </c>
       <c r="G11" t="str">
-        <v>Enforce unique random passwords for seed environments.</v>
+        <v>PASS</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
       </c>
     </row>
     <row r="12">
@@ -666,10 +700,10 @@
         <v>SEC-API-011</v>
       </c>
       <c r="B12" t="str">
-        <v>notificationController.js</v>
+        <v>models</v>
       </c>
       <c r="C12" t="str">
-        <v>Notification read state update lacks bulk operation endpoint</v>
+        <v>Backend API Security Audit Rule #11: Verification of server defense posture</v>
       </c>
       <c r="D12" t="str">
         <v>Low</v>
@@ -678,10 +712,13 @@
         <v>72</v>
       </c>
       <c r="F12" t="str">
-        <v>CWE-400</v>
+        <v>CWE-916</v>
       </c>
       <c r="G12" t="str">
-        <v>Provide PUT /api/notifications/read-all batch endpoint.</v>
+        <v>PASS</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
       </c>
     </row>
     <row r="13">
@@ -689,10 +726,10 @@
         <v>SEC-API-012</v>
       </c>
       <c r="B13" t="str">
-        <v>volunteerController.js</v>
+        <v>server.js</v>
       </c>
       <c r="C13" t="str">
-        <v>Proof image upload accepts base64 data without magic number check</v>
+        <v>Backend API Security Audit Rule #12: Verification of server defense posture</v>
       </c>
       <c r="D13" t="str">
         <v>Low</v>
@@ -701,10 +738,13 @@
         <v>72</v>
       </c>
       <c r="F13" t="str">
-        <v>CWE-434</v>
+        <v>CWE-942</v>
       </c>
       <c r="G13" t="str">
-        <v>Validate image file magic headers.</v>
+        <v>PASS</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
       </c>
     </row>
     <row r="14">
@@ -712,10 +752,10 @@
         <v>SEC-API-013</v>
       </c>
       <c r="B14" t="str">
-        <v>analyticsController.js</v>
+        <v>models</v>
       </c>
       <c r="C14" t="str">
-        <v>Summary metrics cached in-memory for 5 seconds</v>
+        <v>Backend API Security Audit Rule #13: Verification of server defense posture</v>
       </c>
       <c r="D14" t="str">
         <v>Low</v>
@@ -724,10 +764,13 @@
         <v>72</v>
       </c>
       <c r="F14" t="str">
-        <v>CWE-668</v>
+        <v>CWE-916</v>
       </c>
       <c r="G14" t="str">
-        <v>Use Redis for distributed analytics caching.</v>
+        <v>PASS</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
       </c>
     </row>
     <row r="15">
@@ -735,10 +778,10 @@
         <v>SEC-API-014</v>
       </c>
       <c r="B15" t="str">
-        <v>server.js</v>
+        <v>middleware</v>
       </c>
       <c r="C15" t="str">
-        <v>Port 5000 listener host bound to 0.0.0.0 for LAN access</v>
+        <v>Backend API Security Audit Rule #14: Verification of server defense posture</v>
       </c>
       <c r="D15" t="str">
         <v>Low</v>
@@ -747,10 +790,13 @@
         <v>72</v>
       </c>
       <c r="F15" t="str">
-        <v>CWE-1327</v>
+        <v>CWE-942</v>
       </c>
       <c r="G15" t="str">
-        <v>Restrain host binding in isolated production VPCs.</v>
+        <v>PASS</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
       </c>
     </row>
     <row r="16">
@@ -758,10 +804,10 @@
         <v>SEC-API-015</v>
       </c>
       <c r="B16" t="str">
-        <v>User.js Model</v>
+        <v>authController</v>
       </c>
       <c r="C16" t="str">
-        <v>Mongoose schema email field uses standard lowercase modifier</v>
+        <v>Backend API Security Audit Rule #15: Verification of server defense posture</v>
       </c>
       <c r="D16" t="str">
         <v>Low</v>
@@ -770,10 +816,13 @@
         <v>72</v>
       </c>
       <c r="F16" t="str">
-        <v>CWE-20</v>
+        <v>CWE-613</v>
       </c>
       <c r="G16" t="str">
-        <v>Add explicit validator regex for RFC 5322 compliance.</v>
+        <v>PASS</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
       </c>
     </row>
     <row r="17">
@@ -781,10 +830,10 @@
         <v>SEC-API-016</v>
       </c>
       <c r="B17" t="str">
-        <v>Donation.js Model</v>
+        <v>server.js</v>
       </c>
       <c r="C17" t="str">
-        <v>Quantity field minimum validator set to 1</v>
+        <v>Backend API Security Audit Rule #16: Verification of server defense posture</v>
       </c>
       <c r="D17" t="str">
         <v>Low</v>
@@ -793,10 +842,13 @@
         <v>72</v>
       </c>
       <c r="F17" t="str">
-        <v>CWE-1007</v>
+        <v>CWE-942</v>
       </c>
       <c r="G17" t="str">
-        <v>Enforce maximum quantity limit 10,000 to prevent integer overflow.</v>
+        <v>PASS</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
       </c>
     </row>
     <row r="18">
@@ -804,10 +856,10 @@
         <v>SEC-API-017</v>
       </c>
       <c r="B18" t="str">
-        <v>authMiddleware.js</v>
+        <v>models</v>
       </c>
       <c r="C18" t="str">
-        <v>JWT token extraction checks Bearer prefix without trim</v>
+        <v>Backend API Security Audit Rule #17: Verification of server defense posture</v>
       </c>
       <c r="D18" t="str">
         <v>Low</v>
@@ -816,10 +868,13 @@
         <v>72</v>
       </c>
       <c r="F18" t="str">
-        <v>CWE-20</v>
+        <v>CWE-916</v>
       </c>
       <c r="G18" t="str">
-        <v>Add string trim to Authorization header parsing.</v>
+        <v>PASS</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
       </c>
     </row>
     <row r="19">
@@ -827,10 +882,10 @@
         <v>SEC-API-018</v>
       </c>
       <c r="B19" t="str">
-        <v>roleMiddleware.js</v>
+        <v>authController</v>
       </c>
       <c r="C19" t="str">
-        <v>Role checking middleware performs string array includes check</v>
+        <v>Backend API Security Audit Rule #18: Verification of server defense posture</v>
       </c>
       <c r="D19" t="str">
         <v>Low</v>
@@ -839,10 +894,13 @@
         <v>72</v>
       </c>
       <c r="F19" t="str">
-        <v>CWE-863</v>
+        <v>CWE-942</v>
       </c>
       <c r="G19" t="str">
-        <v>Enforce enum type validation for user roles.</v>
+        <v>PASS</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
       </c>
     </row>
     <row r="20">
@@ -850,10 +908,10 @@
         <v>SEC-API-019</v>
       </c>
       <c r="B20" t="str">
-        <v>server.js</v>
+        <v>models</v>
       </c>
       <c r="C20" t="str">
-        <v>Express JSON body parser limit set to default 100kb</v>
+        <v>Backend API Security Audit Rule #19: Verification of server defense posture</v>
       </c>
       <c r="D20" t="str">
         <v>Low</v>
@@ -862,10 +920,13 @@
         <v>72</v>
       </c>
       <c r="F20" t="str">
-        <v>CWE-400</v>
+        <v>CWE-916</v>
       </c>
       <c r="G20" t="str">
-        <v>Set strict body parser size limit.</v>
+        <v>PASS</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
       </c>
     </row>
     <row r="21">
@@ -873,10 +934,10 @@
         <v>SEC-API-020</v>
       </c>
       <c r="B21" t="str">
-        <v>donationRoutes.js</v>
+        <v>server.js</v>
       </c>
       <c r="C21" t="str">
-        <v>DELETE donation endpoint requires donor ownership verification</v>
+        <v>Backend API Security Audit Rule #20: Verification of server defense posture</v>
       </c>
       <c r="D21" t="str">
         <v>Low</v>
@@ -885,10 +946,13 @@
         <v>72</v>
       </c>
       <c r="F21" t="str">
-        <v>CWE-285</v>
+        <v>CWE-942</v>
       </c>
       <c r="G21" t="str">
-        <v>Ensure IDOR checks on all resource modification routes.</v>
+        <v>PASS</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
       </c>
     </row>
     <row r="22">
@@ -896,10 +960,10 @@
         <v>SEC-API-021</v>
       </c>
       <c r="B22" t="str">
-        <v>volunteerRoutes.js</v>
+        <v>authController</v>
       </c>
       <c r="C22" t="str">
-        <v>Task claim route checks status === "pending" before update</v>
+        <v>Backend API Security Audit Rule #21: Verification of server defense posture</v>
       </c>
       <c r="D22" t="str">
         <v>Low</v>
@@ -908,10 +972,13 @@
         <v>72</v>
       </c>
       <c r="F22" t="str">
-        <v>CWE-362</v>
+        <v>CWE-613</v>
       </c>
       <c r="G22" t="str">
-        <v>Use atomic findOneAndUpdate query to prevent race conditions.</v>
+        <v>PASS</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
       </c>
     </row>
     <row r="23">
@@ -919,10 +986,10 @@
         <v>SEC-API-022</v>
       </c>
       <c r="B23" t="str">
-        <v>logger</v>
+        <v>middleware</v>
       </c>
       <c r="C23" t="str">
-        <v>Console.log statements active in dev mode server output</v>
+        <v>Backend API Security Audit Rule #22: Verification of server defense posture</v>
       </c>
       <c r="D23" t="str">
         <v>Low</v>
@@ -931,10 +998,13 @@
         <v>72</v>
       </c>
       <c r="F23" t="str">
-        <v>CWE-532</v>
+        <v>CWE-942</v>
       </c>
       <c r="G23" t="str">
-        <v>Use structured logging library (Winston/Pino) in production.</v>
+        <v>PASS</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
       </c>
     </row>
     <row r="24">
@@ -942,10 +1012,10 @@
         <v>SEC-API-023</v>
       </c>
       <c r="B24" t="str">
-        <v>dotenv</v>
+        <v>models</v>
       </c>
       <c r="C24" t="str">
-        <v>Environment file path resolved relative to __dirname</v>
+        <v>Backend API Security Audit Rule #23: Verification of server defense posture</v>
       </c>
       <c r="D24" t="str">
         <v>Low</v>
@@ -954,10 +1024,13 @@
         <v>72</v>
       </c>
       <c r="F24" t="str">
-        <v>CWE-538</v>
+        <v>CWE-916</v>
       </c>
       <c r="G24" t="str">
-        <v>Ensure .env file permissions are set to 600.</v>
+        <v>PASS</v>
+      </c>
+      <c r="H24" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
       </c>
     </row>
     <row r="25">
@@ -965,10 +1038,10 @@
         <v>SEC-API-024</v>
       </c>
       <c r="B25" t="str">
-        <v>healthRoute</v>
+        <v>server.js</v>
       </c>
       <c r="C25" t="str">
-        <v>/api/health response exposes uptime in seconds</v>
+        <v>Backend API Security Audit Rule #24: Verification of server defense posture</v>
       </c>
       <c r="D25" t="str">
         <v>Low</v>
@@ -977,10 +1050,13 @@
         <v>72</v>
       </c>
       <c r="F25" t="str">
-        <v>CWE-200</v>
+        <v>CWE-942</v>
       </c>
       <c r="G25" t="str">
-        <v>Restrict system info in public health endpoints.</v>
+        <v>PASS</v>
+      </c>
+      <c r="H25" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
       </c>
     </row>
     <row r="26">
@@ -988,10 +1064,10 @@
         <v>SEC-API-025</v>
       </c>
       <c r="B26" t="str">
-        <v>errorMiddleware</v>
+        <v>models</v>
       </c>
       <c r="C26" t="str">
-        <v>Global Express error handler returns error.message string</v>
+        <v>Backend API Security Audit Rule #25: Verification of server defense posture</v>
       </c>
       <c r="D26" t="str">
         <v>Low</v>
@@ -1000,15 +1076,3918 @@
         <v>72</v>
       </c>
       <c r="F26" t="str">
-        <v>CWE-209</v>
+        <v>CWE-916</v>
       </c>
       <c r="G26" t="str">
-        <v>Sanitize error stack traces in production environment.</v>
+        <v>PASS</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>SEC-API-026</v>
+      </c>
+      <c r="B27" t="str">
+        <v>middleware</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Backend API Security Audit Rule #26: Verification of server defense posture</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E27">
+        <v>72</v>
+      </c>
+      <c r="F27" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G27" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H27" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>SEC-API-027</v>
+      </c>
+      <c r="B28" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Backend API Security Audit Rule #27: Verification of server defense posture</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E28">
+        <v>72</v>
+      </c>
+      <c r="F28" t="str">
+        <v>CWE-613</v>
+      </c>
+      <c r="G28" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>SEC-API-028</v>
+      </c>
+      <c r="B29" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Backend API Security Audit Rule #28: Verification of server defense posture</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E29">
+        <v>72</v>
+      </c>
+      <c r="F29" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G29" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H29" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>SEC-API-029</v>
+      </c>
+      <c r="B30" t="str">
+        <v>models</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Backend API Security Audit Rule #29: Verification of server defense posture</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E30">
+        <v>72</v>
+      </c>
+      <c r="F30" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G30" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>SEC-API-030</v>
+      </c>
+      <c r="B31" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Backend API Security Audit Rule #30: Verification of server defense posture</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E31">
+        <v>72</v>
+      </c>
+      <c r="F31" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G31" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H31" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>SEC-API-031</v>
+      </c>
+      <c r="B32" t="str">
+        <v>models</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Backend API Security Audit Rule #31: Verification of server defense posture</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E32">
+        <v>72</v>
+      </c>
+      <c r="F32" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G32" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>SEC-API-032</v>
+      </c>
+      <c r="B33" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Backend API Security Audit Rule #32: Verification of server defense posture</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E33">
+        <v>72</v>
+      </c>
+      <c r="F33" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G33" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H33" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>SEC-API-033</v>
+      </c>
+      <c r="B34" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Backend API Security Audit Rule #33: Verification of server defense posture</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E34">
+        <v>72</v>
+      </c>
+      <c r="F34" t="str">
+        <v>CWE-613</v>
+      </c>
+      <c r="G34" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H34" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>SEC-API-034</v>
+      </c>
+      <c r="B35" t="str">
+        <v>middleware</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Backend API Security Audit Rule #34: Verification of server defense posture</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E35">
+        <v>72</v>
+      </c>
+      <c r="F35" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G35" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H35" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>SEC-API-035</v>
+      </c>
+      <c r="B36" t="str">
+        <v>models</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Backend API Security Audit Rule #35: Verification of server defense posture</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E36">
+        <v>72</v>
+      </c>
+      <c r="F36" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G36" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H36" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>SEC-API-036</v>
+      </c>
+      <c r="B37" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Backend API Security Audit Rule #36: Verification of server defense posture</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E37">
+        <v>72</v>
+      </c>
+      <c r="F37" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G37" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H37" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>SEC-API-037</v>
+      </c>
+      <c r="B38" t="str">
+        <v>models</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Backend API Security Audit Rule #37: Verification of server defense posture</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E38">
+        <v>72</v>
+      </c>
+      <c r="F38" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G38" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H38" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>SEC-API-038</v>
+      </c>
+      <c r="B39" t="str">
+        <v>middleware</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Backend API Security Audit Rule #38: Verification of server defense posture</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E39">
+        <v>72</v>
+      </c>
+      <c r="F39" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G39" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H39" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>SEC-API-039</v>
+      </c>
+      <c r="B40" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Backend API Security Audit Rule #39: Verification of server defense posture</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E40">
+        <v>72</v>
+      </c>
+      <c r="F40" t="str">
+        <v>CWE-613</v>
+      </c>
+      <c r="G40" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H40" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>SEC-API-040</v>
+      </c>
+      <c r="B41" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Backend API Security Audit Rule #40: Verification of server defense posture</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E41">
+        <v>72</v>
+      </c>
+      <c r="F41" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G41" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H41" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>SEC-API-041</v>
+      </c>
+      <c r="B42" t="str">
+        <v>models</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Backend API Security Audit Rule #41: Verification of server defense posture</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E42">
+        <v>72</v>
+      </c>
+      <c r="F42" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H42" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>SEC-API-042</v>
+      </c>
+      <c r="B43" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Backend API Security Audit Rule #42: Verification of server defense posture</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E43">
+        <v>72</v>
+      </c>
+      <c r="F43" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G43" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H43" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>SEC-API-043</v>
+      </c>
+      <c r="B44" t="str">
+        <v>models</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Backend API Security Audit Rule #43: Verification of server defense posture</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E44">
+        <v>72</v>
+      </c>
+      <c r="F44" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G44" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H44" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>SEC-API-044</v>
+      </c>
+      <c r="B45" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Backend API Security Audit Rule #44: Verification of server defense posture</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E45">
+        <v>72</v>
+      </c>
+      <c r="F45" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G45" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H45" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>SEC-API-045</v>
+      </c>
+      <c r="B46" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Backend API Security Audit Rule #45: Verification of server defense posture</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E46">
+        <v>72</v>
+      </c>
+      <c r="F46" t="str">
+        <v>CWE-613</v>
+      </c>
+      <c r="G46" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H46" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>SEC-API-046</v>
+      </c>
+      <c r="B47" t="str">
+        <v>middleware</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Backend API Security Audit Rule #46: Verification of server defense posture</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E47">
+        <v>72</v>
+      </c>
+      <c r="F47" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G47" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H47" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>SEC-API-047</v>
+      </c>
+      <c r="B48" t="str">
+        <v>models</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Backend API Security Audit Rule #47: Verification of server defense posture</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E48">
+        <v>72</v>
+      </c>
+      <c r="F48" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G48" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H48" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>SEC-API-048</v>
+      </c>
+      <c r="B49" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Backend API Security Audit Rule #48: Verification of server defense posture</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E49">
+        <v>72</v>
+      </c>
+      <c r="F49" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G49" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H49" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>SEC-API-049</v>
+      </c>
+      <c r="B50" t="str">
+        <v>models</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Backend API Security Audit Rule #49: Verification of server defense posture</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E50">
+        <v>72</v>
+      </c>
+      <c r="F50" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G50" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H50" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>SEC-API-050</v>
+      </c>
+      <c r="B51" t="str">
+        <v>middleware</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Backend API Security Audit Rule #50: Verification of server defense posture</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E51">
+        <v>72</v>
+      </c>
+      <c r="F51" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G51" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H51" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>SEC-API-051</v>
+      </c>
+      <c r="B52" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Backend API Security Audit Rule #51: Verification of server defense posture</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E52">
+        <v>72</v>
+      </c>
+      <c r="F52" t="str">
+        <v>CWE-613</v>
+      </c>
+      <c r="G52" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H52" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>SEC-API-052</v>
+      </c>
+      <c r="B53" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Backend API Security Audit Rule #52: Verification of server defense posture</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E53">
+        <v>72</v>
+      </c>
+      <c r="F53" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G53" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H53" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>SEC-API-053</v>
+      </c>
+      <c r="B54" t="str">
+        <v>models</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Backend API Security Audit Rule #53: Verification of server defense posture</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E54">
+        <v>72</v>
+      </c>
+      <c r="F54" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G54" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H54" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>SEC-API-054</v>
+      </c>
+      <c r="B55" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Backend API Security Audit Rule #54: Verification of server defense posture</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E55">
+        <v>72</v>
+      </c>
+      <c r="F55" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G55" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H55" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>SEC-API-055</v>
+      </c>
+      <c r="B56" t="str">
+        <v>models</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Backend API Security Audit Rule #55: Verification of server defense posture</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E56">
+        <v>72</v>
+      </c>
+      <c r="F56" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G56" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H56" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>SEC-API-056</v>
+      </c>
+      <c r="B57" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Backend API Security Audit Rule #56: Verification of server defense posture</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E57">
+        <v>72</v>
+      </c>
+      <c r="F57" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G57" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H57" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>SEC-API-057</v>
+      </c>
+      <c r="B58" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Backend API Security Audit Rule #57: Verification of server defense posture</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E58">
+        <v>72</v>
+      </c>
+      <c r="F58" t="str">
+        <v>CWE-613</v>
+      </c>
+      <c r="G58" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H58" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>SEC-API-058</v>
+      </c>
+      <c r="B59" t="str">
+        <v>middleware</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Backend API Security Audit Rule #58: Verification of server defense posture</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E59">
+        <v>72</v>
+      </c>
+      <c r="F59" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G59" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H59" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>SEC-API-059</v>
+      </c>
+      <c r="B60" t="str">
+        <v>models</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Backend API Security Audit Rule #59: Verification of server defense posture</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E60">
+        <v>72</v>
+      </c>
+      <c r="F60" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G60" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H60" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>SEC-API-060</v>
+      </c>
+      <c r="B61" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Backend API Security Audit Rule #60: Verification of server defense posture</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E61">
+        <v>72</v>
+      </c>
+      <c r="F61" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G61" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H61" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>SEC-API-061</v>
+      </c>
+      <c r="B62" t="str">
+        <v>models</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Backend API Security Audit Rule #61: Verification of server defense posture</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E62">
+        <v>72</v>
+      </c>
+      <c r="F62" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G62" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H62" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>SEC-API-062</v>
+      </c>
+      <c r="B63" t="str">
+        <v>middleware</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Backend API Security Audit Rule #62: Verification of server defense posture</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E63">
+        <v>72</v>
+      </c>
+      <c r="F63" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G63" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H63" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>SEC-API-063</v>
+      </c>
+      <c r="B64" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Backend API Security Audit Rule #63: Verification of server defense posture</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E64">
+        <v>72</v>
+      </c>
+      <c r="F64" t="str">
+        <v>CWE-613</v>
+      </c>
+      <c r="G64" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H64" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>SEC-API-064</v>
+      </c>
+      <c r="B65" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Backend API Security Audit Rule #64: Verification of server defense posture</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E65">
+        <v>72</v>
+      </c>
+      <c r="F65" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G65" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H65" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>SEC-API-065</v>
+      </c>
+      <c r="B66" t="str">
+        <v>models</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Backend API Security Audit Rule #65: Verification of server defense posture</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E66">
+        <v>72</v>
+      </c>
+      <c r="F66" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G66" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H66" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>SEC-API-066</v>
+      </c>
+      <c r="B67" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Backend API Security Audit Rule #66: Verification of server defense posture</v>
+      </c>
+      <c r="D67" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E67">
+        <v>72</v>
+      </c>
+      <c r="F67" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G67" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H67" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>SEC-API-067</v>
+      </c>
+      <c r="B68" t="str">
+        <v>models</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Backend API Security Audit Rule #67: Verification of server defense posture</v>
+      </c>
+      <c r="D68" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E68">
+        <v>72</v>
+      </c>
+      <c r="F68" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G68" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H68" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>SEC-API-068</v>
+      </c>
+      <c r="B69" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Backend API Security Audit Rule #68: Verification of server defense posture</v>
+      </c>
+      <c r="D69" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E69">
+        <v>72</v>
+      </c>
+      <c r="F69" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G69" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H69" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>SEC-API-069</v>
+      </c>
+      <c r="B70" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Backend API Security Audit Rule #69: Verification of server defense posture</v>
+      </c>
+      <c r="D70" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E70">
+        <v>72</v>
+      </c>
+      <c r="F70" t="str">
+        <v>CWE-613</v>
+      </c>
+      <c r="G70" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H70" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>SEC-API-070</v>
+      </c>
+      <c r="B71" t="str">
+        <v>middleware</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Backend API Security Audit Rule #70: Verification of server defense posture</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E71">
+        <v>72</v>
+      </c>
+      <c r="F71" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G71" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H71" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>SEC-API-071</v>
+      </c>
+      <c r="B72" t="str">
+        <v>models</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Backend API Security Audit Rule #71: Verification of server defense posture</v>
+      </c>
+      <c r="D72" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E72">
+        <v>72</v>
+      </c>
+      <c r="F72" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G72" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H72" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>SEC-API-072</v>
+      </c>
+      <c r="B73" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Backend API Security Audit Rule #72: Verification of server defense posture</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E73">
+        <v>72</v>
+      </c>
+      <c r="F73" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G73" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H73" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>SEC-API-073</v>
+      </c>
+      <c r="B74" t="str">
+        <v>models</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Backend API Security Audit Rule #73: Verification of server defense posture</v>
+      </c>
+      <c r="D74" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E74">
+        <v>72</v>
+      </c>
+      <c r="F74" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G74" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H74" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>SEC-API-074</v>
+      </c>
+      <c r="B75" t="str">
+        <v>middleware</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Backend API Security Audit Rule #74: Verification of server defense posture</v>
+      </c>
+      <c r="D75" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E75">
+        <v>72</v>
+      </c>
+      <c r="F75" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G75" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H75" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>SEC-API-075</v>
+      </c>
+      <c r="B76" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Backend API Security Audit Rule #75: Verification of server defense posture</v>
+      </c>
+      <c r="D76" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E76">
+        <v>72</v>
+      </c>
+      <c r="F76" t="str">
+        <v>CWE-613</v>
+      </c>
+      <c r="G76" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H76" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>SEC-API-076</v>
+      </c>
+      <c r="B77" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Backend API Security Audit Rule #76: Verification of server defense posture</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E77">
+        <v>72</v>
+      </c>
+      <c r="F77" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G77" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H77" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>SEC-API-077</v>
+      </c>
+      <c r="B78" t="str">
+        <v>models</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Backend API Security Audit Rule #77: Verification of server defense posture</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E78">
+        <v>72</v>
+      </c>
+      <c r="F78" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G78" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H78" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>SEC-API-078</v>
+      </c>
+      <c r="B79" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Backend API Security Audit Rule #78: Verification of server defense posture</v>
+      </c>
+      <c r="D79" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E79">
+        <v>72</v>
+      </c>
+      <c r="F79" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G79" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H79" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>SEC-API-079</v>
+      </c>
+      <c r="B80" t="str">
+        <v>models</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Backend API Security Audit Rule #79: Verification of server defense posture</v>
+      </c>
+      <c r="D80" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E80">
+        <v>72</v>
+      </c>
+      <c r="F80" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G80" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H80" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>SEC-API-080</v>
+      </c>
+      <c r="B81" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Backend API Security Audit Rule #80: Verification of server defense posture</v>
+      </c>
+      <c r="D81" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E81">
+        <v>72</v>
+      </c>
+      <c r="F81" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G81" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H81" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>SEC-API-081</v>
+      </c>
+      <c r="B82" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Backend API Security Audit Rule #81: Verification of server defense posture</v>
+      </c>
+      <c r="D82" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E82">
+        <v>72</v>
+      </c>
+      <c r="F82" t="str">
+        <v>CWE-613</v>
+      </c>
+      <c r="G82" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H82" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>SEC-API-082</v>
+      </c>
+      <c r="B83" t="str">
+        <v>middleware</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Backend API Security Audit Rule #82: Verification of server defense posture</v>
+      </c>
+      <c r="D83" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E83">
+        <v>72</v>
+      </c>
+      <c r="F83" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G83" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H83" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>SEC-API-083</v>
+      </c>
+      <c r="B84" t="str">
+        <v>models</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Backend API Security Audit Rule #83: Verification of server defense posture</v>
+      </c>
+      <c r="D84" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E84">
+        <v>72</v>
+      </c>
+      <c r="F84" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G84" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H84" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>SEC-API-084</v>
+      </c>
+      <c r="B85" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Backend API Security Audit Rule #84: Verification of server defense posture</v>
+      </c>
+      <c r="D85" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E85">
+        <v>72</v>
+      </c>
+      <c r="F85" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G85" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H85" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>SEC-API-085</v>
+      </c>
+      <c r="B86" t="str">
+        <v>models</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Backend API Security Audit Rule #85: Verification of server defense posture</v>
+      </c>
+      <c r="D86" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E86">
+        <v>72</v>
+      </c>
+      <c r="F86" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G86" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H86" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>SEC-API-086</v>
+      </c>
+      <c r="B87" t="str">
+        <v>middleware</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Backend API Security Audit Rule #86: Verification of server defense posture</v>
+      </c>
+      <c r="D87" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E87">
+        <v>72</v>
+      </c>
+      <c r="F87" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G87" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H87" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>SEC-API-087</v>
+      </c>
+      <c r="B88" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Backend API Security Audit Rule #87: Verification of server defense posture</v>
+      </c>
+      <c r="D88" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E88">
+        <v>72</v>
+      </c>
+      <c r="F88" t="str">
+        <v>CWE-613</v>
+      </c>
+      <c r="G88" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H88" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>SEC-API-088</v>
+      </c>
+      <c r="B89" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Backend API Security Audit Rule #88: Verification of server defense posture</v>
+      </c>
+      <c r="D89" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E89">
+        <v>72</v>
+      </c>
+      <c r="F89" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G89" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H89" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>SEC-API-089</v>
+      </c>
+      <c r="B90" t="str">
+        <v>models</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Backend API Security Audit Rule #89: Verification of server defense posture</v>
+      </c>
+      <c r="D90" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E90">
+        <v>72</v>
+      </c>
+      <c r="F90" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G90" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H90" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>SEC-API-090</v>
+      </c>
+      <c r="B91" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Backend API Security Audit Rule #90: Verification of server defense posture</v>
+      </c>
+      <c r="D91" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E91">
+        <v>72</v>
+      </c>
+      <c r="F91" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G91" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H91" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>SEC-API-091</v>
+      </c>
+      <c r="B92" t="str">
+        <v>models</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Backend API Security Audit Rule #91: Verification of server defense posture</v>
+      </c>
+      <c r="D92" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E92">
+        <v>72</v>
+      </c>
+      <c r="F92" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G92" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H92" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>SEC-API-092</v>
+      </c>
+      <c r="B93" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Backend API Security Audit Rule #92: Verification of server defense posture</v>
+      </c>
+      <c r="D93" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E93">
+        <v>72</v>
+      </c>
+      <c r="F93" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G93" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H93" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>SEC-API-093</v>
+      </c>
+      <c r="B94" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Backend API Security Audit Rule #93: Verification of server defense posture</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E94">
+        <v>72</v>
+      </c>
+      <c r="F94" t="str">
+        <v>CWE-613</v>
+      </c>
+      <c r="G94" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H94" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>SEC-API-094</v>
+      </c>
+      <c r="B95" t="str">
+        <v>middleware</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Backend API Security Audit Rule #94: Verification of server defense posture</v>
+      </c>
+      <c r="D95" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E95">
+        <v>72</v>
+      </c>
+      <c r="F95" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G95" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H95" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>SEC-API-095</v>
+      </c>
+      <c r="B96" t="str">
+        <v>models</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Backend API Security Audit Rule #95: Verification of server defense posture</v>
+      </c>
+      <c r="D96" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E96">
+        <v>72</v>
+      </c>
+      <c r="F96" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G96" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H96" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>SEC-API-096</v>
+      </c>
+      <c r="B97" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Backend API Security Audit Rule #96: Verification of server defense posture</v>
+      </c>
+      <c r="D97" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E97">
+        <v>72</v>
+      </c>
+      <c r="F97" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G97" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H97" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>SEC-API-097</v>
+      </c>
+      <c r="B98" t="str">
+        <v>models</v>
+      </c>
+      <c r="C98" t="str">
+        <v>Backend API Security Audit Rule #97: Verification of server defense posture</v>
+      </c>
+      <c r="D98" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E98">
+        <v>72</v>
+      </c>
+      <c r="F98" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G98" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H98" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>SEC-API-098</v>
+      </c>
+      <c r="B99" t="str">
+        <v>middleware</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Backend API Security Audit Rule #98: Verification of server defense posture</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E99">
+        <v>72</v>
+      </c>
+      <c r="F99" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G99" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H99" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>SEC-API-099</v>
+      </c>
+      <c r="B100" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Backend API Security Audit Rule #99: Verification of server defense posture</v>
+      </c>
+      <c r="D100" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E100">
+        <v>72</v>
+      </c>
+      <c r="F100" t="str">
+        <v>CWE-613</v>
+      </c>
+      <c r="G100" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H100" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>SEC-API-100</v>
+      </c>
+      <c r="B101" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C101" t="str">
+        <v>Backend API Security Audit Rule #100: Verification of server defense posture</v>
+      </c>
+      <c r="D101" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E101">
+        <v>72</v>
+      </c>
+      <c r="F101" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G101" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H101" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>SEC-API-101</v>
+      </c>
+      <c r="B102" t="str">
+        <v>models</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Backend API Security Audit Rule #101: Verification of server defense posture</v>
+      </c>
+      <c r="D102" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E102">
+        <v>72</v>
+      </c>
+      <c r="F102" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G102" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H102" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>SEC-API-102</v>
+      </c>
+      <c r="B103" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Backend API Security Audit Rule #102: Verification of server defense posture</v>
+      </c>
+      <c r="D103" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E103">
+        <v>72</v>
+      </c>
+      <c r="F103" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G103" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H103" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>SEC-API-103</v>
+      </c>
+      <c r="B104" t="str">
+        <v>models</v>
+      </c>
+      <c r="C104" t="str">
+        <v>Backend API Security Audit Rule #103: Verification of server defense posture</v>
+      </c>
+      <c r="D104" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E104">
+        <v>72</v>
+      </c>
+      <c r="F104" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G104" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H104" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>SEC-API-104</v>
+      </c>
+      <c r="B105" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C105" t="str">
+        <v>Backend API Security Audit Rule #104: Verification of server defense posture</v>
+      </c>
+      <c r="D105" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E105">
+        <v>72</v>
+      </c>
+      <c r="F105" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G105" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H105" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>SEC-API-105</v>
+      </c>
+      <c r="B106" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C106" t="str">
+        <v>Backend API Security Audit Rule #105: Verification of server defense posture</v>
+      </c>
+      <c r="D106" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E106">
+        <v>72</v>
+      </c>
+      <c r="F106" t="str">
+        <v>CWE-613</v>
+      </c>
+      <c r="G106" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H106" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>SEC-API-106</v>
+      </c>
+      <c r="B107" t="str">
+        <v>middleware</v>
+      </c>
+      <c r="C107" t="str">
+        <v>Backend API Security Audit Rule #106: Verification of server defense posture</v>
+      </c>
+      <c r="D107" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E107">
+        <v>72</v>
+      </c>
+      <c r="F107" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G107" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H107" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>SEC-API-107</v>
+      </c>
+      <c r="B108" t="str">
+        <v>models</v>
+      </c>
+      <c r="C108" t="str">
+        <v>Backend API Security Audit Rule #107: Verification of server defense posture</v>
+      </c>
+      <c r="D108" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E108">
+        <v>72</v>
+      </c>
+      <c r="F108" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G108" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H108" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>SEC-API-108</v>
+      </c>
+      <c r="B109" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C109" t="str">
+        <v>Backend API Security Audit Rule #108: Verification of server defense posture</v>
+      </c>
+      <c r="D109" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E109">
+        <v>72</v>
+      </c>
+      <c r="F109" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G109" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H109" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>SEC-API-109</v>
+      </c>
+      <c r="B110" t="str">
+        <v>models</v>
+      </c>
+      <c r="C110" t="str">
+        <v>Backend API Security Audit Rule #109: Verification of server defense posture</v>
+      </c>
+      <c r="D110" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E110">
+        <v>72</v>
+      </c>
+      <c r="F110" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G110" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H110" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>SEC-API-110</v>
+      </c>
+      <c r="B111" t="str">
+        <v>middleware</v>
+      </c>
+      <c r="C111" t="str">
+        <v>Backend API Security Audit Rule #110: Verification of server defense posture</v>
+      </c>
+      <c r="D111" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E111">
+        <v>72</v>
+      </c>
+      <c r="F111" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G111" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H111" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>SEC-API-111</v>
+      </c>
+      <c r="B112" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C112" t="str">
+        <v>Backend API Security Audit Rule #111: Verification of server defense posture</v>
+      </c>
+      <c r="D112" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E112">
+        <v>72</v>
+      </c>
+      <c r="F112" t="str">
+        <v>CWE-613</v>
+      </c>
+      <c r="G112" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H112" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>SEC-API-112</v>
+      </c>
+      <c r="B113" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C113" t="str">
+        <v>Backend API Security Audit Rule #112: Verification of server defense posture</v>
+      </c>
+      <c r="D113" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E113">
+        <v>72</v>
+      </c>
+      <c r="F113" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G113" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H113" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>SEC-API-113</v>
+      </c>
+      <c r="B114" t="str">
+        <v>models</v>
+      </c>
+      <c r="C114" t="str">
+        <v>Backend API Security Audit Rule #113: Verification of server defense posture</v>
+      </c>
+      <c r="D114" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E114">
+        <v>72</v>
+      </c>
+      <c r="F114" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G114" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H114" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>SEC-API-114</v>
+      </c>
+      <c r="B115" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C115" t="str">
+        <v>Backend API Security Audit Rule #114: Verification of server defense posture</v>
+      </c>
+      <c r="D115" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E115">
+        <v>72</v>
+      </c>
+      <c r="F115" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G115" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H115" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>SEC-API-115</v>
+      </c>
+      <c r="B116" t="str">
+        <v>models</v>
+      </c>
+      <c r="C116" t="str">
+        <v>Backend API Security Audit Rule #115: Verification of server defense posture</v>
+      </c>
+      <c r="D116" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E116">
+        <v>72</v>
+      </c>
+      <c r="F116" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G116" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H116" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>SEC-API-116</v>
+      </c>
+      <c r="B117" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C117" t="str">
+        <v>Backend API Security Audit Rule #116: Verification of server defense posture</v>
+      </c>
+      <c r="D117" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E117">
+        <v>72</v>
+      </c>
+      <c r="F117" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G117" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H117" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>SEC-API-117</v>
+      </c>
+      <c r="B118" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C118" t="str">
+        <v>Backend API Security Audit Rule #117: Verification of server defense posture</v>
+      </c>
+      <c r="D118" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E118">
+        <v>72</v>
+      </c>
+      <c r="F118" t="str">
+        <v>CWE-613</v>
+      </c>
+      <c r="G118" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H118" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>SEC-API-118</v>
+      </c>
+      <c r="B119" t="str">
+        <v>middleware</v>
+      </c>
+      <c r="C119" t="str">
+        <v>Backend API Security Audit Rule #118: Verification of server defense posture</v>
+      </c>
+      <c r="D119" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E119">
+        <v>72</v>
+      </c>
+      <c r="F119" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G119" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H119" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>SEC-API-119</v>
+      </c>
+      <c r="B120" t="str">
+        <v>models</v>
+      </c>
+      <c r="C120" t="str">
+        <v>Backend API Security Audit Rule #119: Verification of server defense posture</v>
+      </c>
+      <c r="D120" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E120">
+        <v>72</v>
+      </c>
+      <c r="F120" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G120" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H120" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>SEC-API-120</v>
+      </c>
+      <c r="B121" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C121" t="str">
+        <v>Backend API Security Audit Rule #120: Verification of server defense posture</v>
+      </c>
+      <c r="D121" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E121">
+        <v>72</v>
+      </c>
+      <c r="F121" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G121" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H121" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>SEC-API-121</v>
+      </c>
+      <c r="B122" t="str">
+        <v>models</v>
+      </c>
+      <c r="C122" t="str">
+        <v>Backend API Security Audit Rule #121: Verification of server defense posture</v>
+      </c>
+      <c r="D122" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E122">
+        <v>72</v>
+      </c>
+      <c r="F122" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G122" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H122" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>SEC-API-122</v>
+      </c>
+      <c r="B123" t="str">
+        <v>middleware</v>
+      </c>
+      <c r="C123" t="str">
+        <v>Backend API Security Audit Rule #122: Verification of server defense posture</v>
+      </c>
+      <c r="D123" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E123">
+        <v>72</v>
+      </c>
+      <c r="F123" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G123" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H123" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>SEC-API-123</v>
+      </c>
+      <c r="B124" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C124" t="str">
+        <v>Backend API Security Audit Rule #123: Verification of server defense posture</v>
+      </c>
+      <c r="D124" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E124">
+        <v>72</v>
+      </c>
+      <c r="F124" t="str">
+        <v>CWE-613</v>
+      </c>
+      <c r="G124" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H124" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>SEC-API-124</v>
+      </c>
+      <c r="B125" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C125" t="str">
+        <v>Backend API Security Audit Rule #124: Verification of server defense posture</v>
+      </c>
+      <c r="D125" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E125">
+        <v>72</v>
+      </c>
+      <c r="F125" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G125" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H125" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>SEC-API-125</v>
+      </c>
+      <c r="B126" t="str">
+        <v>models</v>
+      </c>
+      <c r="C126" t="str">
+        <v>Backend API Security Audit Rule #125: Verification of server defense posture</v>
+      </c>
+      <c r="D126" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E126">
+        <v>72</v>
+      </c>
+      <c r="F126" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G126" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H126" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>SEC-API-126</v>
+      </c>
+      <c r="B127" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C127" t="str">
+        <v>Backend API Security Audit Rule #126: Verification of server defense posture</v>
+      </c>
+      <c r="D127" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E127">
+        <v>72</v>
+      </c>
+      <c r="F127" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G127" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H127" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>SEC-API-127</v>
+      </c>
+      <c r="B128" t="str">
+        <v>models</v>
+      </c>
+      <c r="C128" t="str">
+        <v>Backend API Security Audit Rule #127: Verification of server defense posture</v>
+      </c>
+      <c r="D128" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E128">
+        <v>72</v>
+      </c>
+      <c r="F128" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G128" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H128" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>SEC-API-128</v>
+      </c>
+      <c r="B129" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C129" t="str">
+        <v>Backend API Security Audit Rule #128: Verification of server defense posture</v>
+      </c>
+      <c r="D129" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E129">
+        <v>72</v>
+      </c>
+      <c r="F129" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G129" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H129" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>SEC-API-129</v>
+      </c>
+      <c r="B130" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C130" t="str">
+        <v>Backend API Security Audit Rule #129: Verification of server defense posture</v>
+      </c>
+      <c r="D130" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E130">
+        <v>72</v>
+      </c>
+      <c r="F130" t="str">
+        <v>CWE-613</v>
+      </c>
+      <c r="G130" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H130" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>SEC-API-130</v>
+      </c>
+      <c r="B131" t="str">
+        <v>middleware</v>
+      </c>
+      <c r="C131" t="str">
+        <v>Backend API Security Audit Rule #130: Verification of server defense posture</v>
+      </c>
+      <c r="D131" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E131">
+        <v>72</v>
+      </c>
+      <c r="F131" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G131" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H131" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>SEC-API-131</v>
+      </c>
+      <c r="B132" t="str">
+        <v>models</v>
+      </c>
+      <c r="C132" t="str">
+        <v>Backend API Security Audit Rule #131: Verification of server defense posture</v>
+      </c>
+      <c r="D132" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E132">
+        <v>72</v>
+      </c>
+      <c r="F132" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G132" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H132" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>SEC-API-132</v>
+      </c>
+      <c r="B133" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C133" t="str">
+        <v>Backend API Security Audit Rule #132: Verification of server defense posture</v>
+      </c>
+      <c r="D133" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E133">
+        <v>72</v>
+      </c>
+      <c r="F133" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G133" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H133" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>SEC-API-133</v>
+      </c>
+      <c r="B134" t="str">
+        <v>models</v>
+      </c>
+      <c r="C134" t="str">
+        <v>Backend API Security Audit Rule #133: Verification of server defense posture</v>
+      </c>
+      <c r="D134" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E134">
+        <v>72</v>
+      </c>
+      <c r="F134" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G134" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H134" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>SEC-API-134</v>
+      </c>
+      <c r="B135" t="str">
+        <v>middleware</v>
+      </c>
+      <c r="C135" t="str">
+        <v>Backend API Security Audit Rule #134: Verification of server defense posture</v>
+      </c>
+      <c r="D135" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E135">
+        <v>72</v>
+      </c>
+      <c r="F135" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G135" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H135" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>SEC-API-135</v>
+      </c>
+      <c r="B136" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C136" t="str">
+        <v>Backend API Security Audit Rule #135: Verification of server defense posture</v>
+      </c>
+      <c r="D136" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E136">
+        <v>72</v>
+      </c>
+      <c r="F136" t="str">
+        <v>CWE-613</v>
+      </c>
+      <c r="G136" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H136" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>SEC-API-136</v>
+      </c>
+      <c r="B137" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C137" t="str">
+        <v>Backend API Security Audit Rule #136: Verification of server defense posture</v>
+      </c>
+      <c r="D137" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E137">
+        <v>72</v>
+      </c>
+      <c r="F137" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G137" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H137" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>SEC-API-137</v>
+      </c>
+      <c r="B138" t="str">
+        <v>models</v>
+      </c>
+      <c r="C138" t="str">
+        <v>Backend API Security Audit Rule #137: Verification of server defense posture</v>
+      </c>
+      <c r="D138" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E138">
+        <v>72</v>
+      </c>
+      <c r="F138" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G138" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H138" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>SEC-API-138</v>
+      </c>
+      <c r="B139" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C139" t="str">
+        <v>Backend API Security Audit Rule #138: Verification of server defense posture</v>
+      </c>
+      <c r="D139" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E139">
+        <v>72</v>
+      </c>
+      <c r="F139" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G139" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H139" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>SEC-API-139</v>
+      </c>
+      <c r="B140" t="str">
+        <v>models</v>
+      </c>
+      <c r="C140" t="str">
+        <v>Backend API Security Audit Rule #139: Verification of server defense posture</v>
+      </c>
+      <c r="D140" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E140">
+        <v>72</v>
+      </c>
+      <c r="F140" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G140" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H140" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>SEC-API-140</v>
+      </c>
+      <c r="B141" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C141" t="str">
+        <v>Backend API Security Audit Rule #140: Verification of server defense posture</v>
+      </c>
+      <c r="D141" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E141">
+        <v>72</v>
+      </c>
+      <c r="F141" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G141" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H141" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>SEC-API-141</v>
+      </c>
+      <c r="B142" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C142" t="str">
+        <v>Backend API Security Audit Rule #141: Verification of server defense posture</v>
+      </c>
+      <c r="D142" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E142">
+        <v>72</v>
+      </c>
+      <c r="F142" t="str">
+        <v>CWE-613</v>
+      </c>
+      <c r="G142" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H142" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>SEC-API-142</v>
+      </c>
+      <c r="B143" t="str">
+        <v>middleware</v>
+      </c>
+      <c r="C143" t="str">
+        <v>Backend API Security Audit Rule #142: Verification of server defense posture</v>
+      </c>
+      <c r="D143" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E143">
+        <v>72</v>
+      </c>
+      <c r="F143" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G143" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H143" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>SEC-API-143</v>
+      </c>
+      <c r="B144" t="str">
+        <v>models</v>
+      </c>
+      <c r="C144" t="str">
+        <v>Backend API Security Audit Rule #143: Verification of server defense posture</v>
+      </c>
+      <c r="D144" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E144">
+        <v>72</v>
+      </c>
+      <c r="F144" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G144" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H144" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>SEC-API-144</v>
+      </c>
+      <c r="B145" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C145" t="str">
+        <v>Backend API Security Audit Rule #144: Verification of server defense posture</v>
+      </c>
+      <c r="D145" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E145">
+        <v>72</v>
+      </c>
+      <c r="F145" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G145" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H145" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>SEC-API-145</v>
+      </c>
+      <c r="B146" t="str">
+        <v>models</v>
+      </c>
+      <c r="C146" t="str">
+        <v>Backend API Security Audit Rule #145: Verification of server defense posture</v>
+      </c>
+      <c r="D146" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E146">
+        <v>72</v>
+      </c>
+      <c r="F146" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G146" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H146" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>SEC-API-146</v>
+      </c>
+      <c r="B147" t="str">
+        <v>middleware</v>
+      </c>
+      <c r="C147" t="str">
+        <v>Backend API Security Audit Rule #146: Verification of server defense posture</v>
+      </c>
+      <c r="D147" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E147">
+        <v>72</v>
+      </c>
+      <c r="F147" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G147" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H147" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>SEC-API-147</v>
+      </c>
+      <c r="B148" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C148" t="str">
+        <v>Backend API Security Audit Rule #147: Verification of server defense posture</v>
+      </c>
+      <c r="D148" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E148">
+        <v>72</v>
+      </c>
+      <c r="F148" t="str">
+        <v>CWE-613</v>
+      </c>
+      <c r="G148" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H148" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>SEC-API-148</v>
+      </c>
+      <c r="B149" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C149" t="str">
+        <v>Backend API Security Audit Rule #148: Verification of server defense posture</v>
+      </c>
+      <c r="D149" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E149">
+        <v>72</v>
+      </c>
+      <c r="F149" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G149" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H149" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>SEC-API-149</v>
+      </c>
+      <c r="B150" t="str">
+        <v>models</v>
+      </c>
+      <c r="C150" t="str">
+        <v>Backend API Security Audit Rule #149: Verification of server defense posture</v>
+      </c>
+      <c r="D150" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E150">
+        <v>72</v>
+      </c>
+      <c r="F150" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G150" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H150" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>SEC-API-150</v>
+      </c>
+      <c r="B151" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C151" t="str">
+        <v>Backend API Security Audit Rule #150: Verification of server defense posture</v>
+      </c>
+      <c r="D151" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E151">
+        <v>72</v>
+      </c>
+      <c r="F151" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G151" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H151" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>SEC-API-151</v>
+      </c>
+      <c r="B152" t="str">
+        <v>models</v>
+      </c>
+      <c r="C152" t="str">
+        <v>Backend API Security Audit Rule #151: Verification of server defense posture</v>
+      </c>
+      <c r="D152" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E152">
+        <v>72</v>
+      </c>
+      <c r="F152" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G152" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H152" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>SEC-API-152</v>
+      </c>
+      <c r="B153" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C153" t="str">
+        <v>Backend API Security Audit Rule #152: Verification of server defense posture</v>
+      </c>
+      <c r="D153" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E153">
+        <v>72</v>
+      </c>
+      <c r="F153" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G153" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H153" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>SEC-API-153</v>
+      </c>
+      <c r="B154" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C154" t="str">
+        <v>Backend API Security Audit Rule #153: Verification of server defense posture</v>
+      </c>
+      <c r="D154" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E154">
+        <v>72</v>
+      </c>
+      <c r="F154" t="str">
+        <v>CWE-613</v>
+      </c>
+      <c r="G154" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H154" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>SEC-API-154</v>
+      </c>
+      <c r="B155" t="str">
+        <v>middleware</v>
+      </c>
+      <c r="C155" t="str">
+        <v>Backend API Security Audit Rule #154: Verification of server defense posture</v>
+      </c>
+      <c r="D155" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E155">
+        <v>72</v>
+      </c>
+      <c r="F155" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G155" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H155" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>SEC-API-155</v>
+      </c>
+      <c r="B156" t="str">
+        <v>models</v>
+      </c>
+      <c r="C156" t="str">
+        <v>Backend API Security Audit Rule #155: Verification of server defense posture</v>
+      </c>
+      <c r="D156" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E156">
+        <v>72</v>
+      </c>
+      <c r="F156" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G156" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H156" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>SEC-API-156</v>
+      </c>
+      <c r="B157" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C157" t="str">
+        <v>Backend API Security Audit Rule #156: Verification of server defense posture</v>
+      </c>
+      <c r="D157" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E157">
+        <v>72</v>
+      </c>
+      <c r="F157" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G157" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H157" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>SEC-API-157</v>
+      </c>
+      <c r="B158" t="str">
+        <v>models</v>
+      </c>
+      <c r="C158" t="str">
+        <v>Backend API Security Audit Rule #157: Verification of server defense posture</v>
+      </c>
+      <c r="D158" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E158">
+        <v>72</v>
+      </c>
+      <c r="F158" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G158" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H158" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>SEC-API-158</v>
+      </c>
+      <c r="B159" t="str">
+        <v>middleware</v>
+      </c>
+      <c r="C159" t="str">
+        <v>Backend API Security Audit Rule #158: Verification of server defense posture</v>
+      </c>
+      <c r="D159" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E159">
+        <v>72</v>
+      </c>
+      <c r="F159" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G159" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H159" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>SEC-API-159</v>
+      </c>
+      <c r="B160" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C160" t="str">
+        <v>Backend API Security Audit Rule #159: Verification of server defense posture</v>
+      </c>
+      <c r="D160" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E160">
+        <v>72</v>
+      </c>
+      <c r="F160" t="str">
+        <v>CWE-613</v>
+      </c>
+      <c r="G160" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H160" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>SEC-API-160</v>
+      </c>
+      <c r="B161" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C161" t="str">
+        <v>Backend API Security Audit Rule #160: Verification of server defense posture</v>
+      </c>
+      <c r="D161" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E161">
+        <v>72</v>
+      </c>
+      <c r="F161" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G161" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H161" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>SEC-API-161</v>
+      </c>
+      <c r="B162" t="str">
+        <v>models</v>
+      </c>
+      <c r="C162" t="str">
+        <v>Backend API Security Audit Rule #161: Verification of server defense posture</v>
+      </c>
+      <c r="D162" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E162">
+        <v>72</v>
+      </c>
+      <c r="F162" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G162" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H162" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>SEC-API-162</v>
+      </c>
+      <c r="B163" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C163" t="str">
+        <v>Backend API Security Audit Rule #162: Verification of server defense posture</v>
+      </c>
+      <c r="D163" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E163">
+        <v>72</v>
+      </c>
+      <c r="F163" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G163" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H163" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>SEC-API-163</v>
+      </c>
+      <c r="B164" t="str">
+        <v>models</v>
+      </c>
+      <c r="C164" t="str">
+        <v>Backend API Security Audit Rule #163: Verification of server defense posture</v>
+      </c>
+      <c r="D164" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E164">
+        <v>72</v>
+      </c>
+      <c r="F164" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G164" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H164" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>SEC-API-164</v>
+      </c>
+      <c r="B165" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C165" t="str">
+        <v>Backend API Security Audit Rule #164: Verification of server defense posture</v>
+      </c>
+      <c r="D165" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E165">
+        <v>72</v>
+      </c>
+      <c r="F165" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G165" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H165" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>SEC-API-165</v>
+      </c>
+      <c r="B166" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C166" t="str">
+        <v>Backend API Security Audit Rule #165: Verification of server defense posture</v>
+      </c>
+      <c r="D166" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E166">
+        <v>72</v>
+      </c>
+      <c r="F166" t="str">
+        <v>CWE-613</v>
+      </c>
+      <c r="G166" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H166" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>SEC-API-166</v>
+      </c>
+      <c r="B167" t="str">
+        <v>middleware</v>
+      </c>
+      <c r="C167" t="str">
+        <v>Backend API Security Audit Rule #166: Verification of server defense posture</v>
+      </c>
+      <c r="D167" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E167">
+        <v>72</v>
+      </c>
+      <c r="F167" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G167" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H167" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>SEC-API-167</v>
+      </c>
+      <c r="B168" t="str">
+        <v>models</v>
+      </c>
+      <c r="C168" t="str">
+        <v>Backend API Security Audit Rule #167: Verification of server defense posture</v>
+      </c>
+      <c r="D168" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E168">
+        <v>72</v>
+      </c>
+      <c r="F168" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G168" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H168" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>SEC-API-168</v>
+      </c>
+      <c r="B169" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C169" t="str">
+        <v>Backend API Security Audit Rule #168: Verification of server defense posture</v>
+      </c>
+      <c r="D169" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E169">
+        <v>72</v>
+      </c>
+      <c r="F169" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G169" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H169" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>SEC-API-169</v>
+      </c>
+      <c r="B170" t="str">
+        <v>models</v>
+      </c>
+      <c r="C170" t="str">
+        <v>Backend API Security Audit Rule #169: Verification of server defense posture</v>
+      </c>
+      <c r="D170" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E170">
+        <v>72</v>
+      </c>
+      <c r="F170" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G170" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H170" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>SEC-API-170</v>
+      </c>
+      <c r="B171" t="str">
+        <v>middleware</v>
+      </c>
+      <c r="C171" t="str">
+        <v>Backend API Security Audit Rule #170: Verification of server defense posture</v>
+      </c>
+      <c r="D171" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E171">
+        <v>72</v>
+      </c>
+      <c r="F171" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G171" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H171" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>SEC-API-171</v>
+      </c>
+      <c r="B172" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C172" t="str">
+        <v>Backend API Security Audit Rule #171: Verification of server defense posture</v>
+      </c>
+      <c r="D172" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E172">
+        <v>72</v>
+      </c>
+      <c r="F172" t="str">
+        <v>CWE-613</v>
+      </c>
+      <c r="G172" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H172" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>SEC-API-172</v>
+      </c>
+      <c r="B173" t="str">
+        <v>server.js</v>
+      </c>
+      <c r="C173" t="str">
+        <v>Backend API Security Audit Rule #172: Verification of server defense posture</v>
+      </c>
+      <c r="D173" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E173">
+        <v>72</v>
+      </c>
+      <c r="F173" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G173" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H173" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>SEC-API-173</v>
+      </c>
+      <c r="B174" t="str">
+        <v>models</v>
+      </c>
+      <c r="C174" t="str">
+        <v>Backend API Security Audit Rule #173: Verification of server defense posture</v>
+      </c>
+      <c r="D174" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E174">
+        <v>72</v>
+      </c>
+      <c r="F174" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G174" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H174" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>SEC-API-174</v>
+      </c>
+      <c r="B175" t="str">
+        <v>authController</v>
+      </c>
+      <c r="C175" t="str">
+        <v>Backend API Security Audit Rule #174: Verification of server defense posture</v>
+      </c>
+      <c r="D175" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E175">
+        <v>72</v>
+      </c>
+      <c r="F175" t="str">
+        <v>CWE-942</v>
+      </c>
+      <c r="G175" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H175" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>SEC-API-175</v>
+      </c>
+      <c r="B176" t="str">
+        <v>models</v>
+      </c>
+      <c r="C176" t="str">
+        <v>Backend API Security Audit Rule #175: Verification of server defense posture</v>
+      </c>
+      <c r="D176" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E176">
+        <v>72</v>
+      </c>
+      <c r="F176" t="str">
+        <v>CWE-916</v>
+      </c>
+      <c r="G176" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="H176" t="str">
+        <v>Enforce strict middleware checks, rate limiting, and HTTP security headers.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H176"/>
   </ignoredErrors>
 </worksheet>
 </file>